--- a/output/2026-10-04_14_Malesia_Sarawak_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-04_14_Malesia_Sarawak_Componentistica_Ventilazione_industriale.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Marketplace B2B MRO registrato MOF (1198228-D), reale e attivo; serve Kuching/Miri/Bintulu ma con logistica consolidata da Peninsular Malaysia, non filiale fisica in Sarawak. Assortimento specifico ventilazione/filtrazione non confermato - canale generico MRO, non specialistico.</t>
+          <t>Marketplace B2B MRO registrato MOF (1198228-D), reale e attivo; serve Kuching/Miri/Bintulu ma con logistica consolidata da Peninsular Malaysia, non filiale fisica in Sarawak. Assortimento specifico ventilazione/filtrazione non confermato - canale generico MRO, non specialistico. [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore cuscinetti/trasmissioni meccaniche (SKF e altri marchi), componentistica industriale affine ma non ventilazione specifica. Confermato da 3 fonti indipendenti.</t>
+          <t>Distributore cuscinetti/trasmissioni meccaniche (SKF e altri marchi), componentistica industriale affine ma non ventilazione specifica. Confermato da 3 fonti indipendenti. [DUPLICATO — vedi anche: 2026-10-01_19_Malesia_Kelantan_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,7 +558,6 @@
           <t>SM-CYCLO (Malaysia) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Kuching, Sarawak (sales office)</t>
@@ -574,7 +573,6 @@
           <t>+60 19-335 0455</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Distributore ufficiale Sumitomo Drive Technologies per Sarawak (riduttori/motoriduttori); componentistica industriale affine, non ventilazione specifica. Nessun sito web dedicato reperito, solo pagine facility su sumitomodrive.com. Email non verificabile da fonte aperta.</t>
@@ -582,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
